--- a/exercisesLifeContingencies/lifeInsurance/makeham_wli.xlsx
+++ b/exercisesLifeContingencies/lifeInsurance/makeham_wli.xlsx
@@ -1,51 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="makeham_wli" sheetId="1" r:id="rId1"/>
+    <sheet name="makeham_wli" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
-  <si>
-    <t>age</t>
-  </si>
-  <si>
-    <t>Ax</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -60,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -376,1059 +420,1067 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B131"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>age</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Ax</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" t="n">
+        <v>0.02131339257431903</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>0.02131339257431903</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
+      <c r="B3" t="n">
         <v>0.02216116127381717</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="n">
         <v>0.02305116984797573</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
+    <row r="5">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="n">
         <v>0.02398549785717418</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
+    <row r="6">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="n">
         <v>0.02496632418118079</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
+    <row r="7">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="n">
         <v>0.02599593138746477</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
+    <row r="8">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="n">
         <v>0.02707671024495758</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
+    <row r="9">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="n">
         <v>0.02821116438192677</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
+    <row r="10">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="n">
         <v>0.02940191508558346</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
+    <row r="11">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="n">
         <v>0.03065170623984182</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
+    <row r="12">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="n">
         <v>0.03196340939627151</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
+    <row r="13">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="n">
         <v>0.03334002897171479</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
-      <c r="A14">
+    <row r="14">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="n">
         <v>0.03478470756425205</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15">
+    <row r="15">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="n">
         <v>0.03630073137717097</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16">
+    <row r="16">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="n">
         <v>0.03789153573830823</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
-      <c r="A17">
+    <row r="17">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="n">
         <v>0.03956071069954484</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
+    <row r="18">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="n">
         <v>0.04131200669833626</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
-      <c r="A19">
+    <row r="19">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="n">
         <v>0.0431493402599024</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
-      <c r="A20">
+    <row r="20">
+      <c r="A20" t="n">
         <v>18</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="n">
         <v>0.04507679971506211</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
-      <c r="A21">
+    <row r="21">
+      <c r="A21" t="n">
         <v>19</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="n">
         <v>0.04709865090463529</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
-      <c r="A22">
+    <row r="22">
+      <c r="A22" t="n">
         <v>20</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="n">
         <v>0.04921934283681906</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
-      <c r="A23">
+    <row r="23">
+      <c r="A23" t="n">
         <v>21</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="n">
         <v>0.05144351325892879</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
-      <c r="A24">
+    <row r="24">
+      <c r="A24" t="n">
         <v>22</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="n">
         <v>0.05377599409934607</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
-      <c r="A25">
+    <row r="25">
+      <c r="A25" t="n">
         <v>23</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="n">
         <v>0.05622181672938697</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
-      <c r="A26">
+    <row r="26">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="n">
         <v>0.05878621698805893</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
-      <c r="A27">
+    <row r="27">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="n">
         <v>0.06147463990526979</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
-      <c r="A28">
+    <row r="28">
+      <c r="A28" t="n">
         <v>26</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="n">
         <v>0.06429274405094447</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
-      <c r="A29">
+    <row r="29">
+      <c r="A29" t="n">
         <v>27</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="n">
         <v>0.06724640542866429</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
-      <c r="A30">
+    <row r="30">
+      <c r="A30" t="n">
         <v>28</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="n">
         <v>0.07034172082282271</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
-      <c r="A31">
+    <row r="31">
+      <c r="A31" t="n">
         <v>29</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="n">
         <v>0.07358501049787318</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
-      <c r="A32">
+    <row r="32">
+      <c r="A32" t="n">
         <v>30</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="n">
         <v>0.07698282013699637</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
-      <c r="A33">
+    <row r="33">
+      <c r="A33" t="n">
         <v>31</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="n">
         <v>0.08054192189542504</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
-      <c r="A34">
+    <row r="34">
+      <c r="A34" t="n">
         <v>32</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="n">
         <v>0.08426931443073285</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
-      <c r="A35">
+    <row r="35">
+      <c r="A35" t="n">
         <v>33</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="n">
         <v>0.08817222175862861</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
-      <c r="A36">
+    <row r="36">
+      <c r="A36" t="n">
         <v>34</v>
       </c>
-      <c r="B36">
+      <c r="B36" t="n">
         <v>0.09225809076823245</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
-      <c r="A37">
+    <row r="37">
+      <c r="A37" t="n">
         <v>35</v>
       </c>
-      <c r="B37">
+      <c r="B37" t="n">
         <v>0.09653458721549465</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
+    <row r="38">
+      <c r="A38" t="n">
         <v>36</v>
       </c>
-      <c r="B38">
+      <c r="B38" t="n">
         <v>0.1010095899974369</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
-      <c r="A39">
+    <row r="39">
+      <c r="A39" t="n">
         <v>37</v>
       </c>
-      <c r="B39">
+      <c r="B39" t="n">
         <v>0.1056911834933572</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
-      <c r="A40">
+    <row r="40">
+      <c r="A40" t="n">
         <v>38</v>
       </c>
-      <c r="B40">
+      <c r="B40" t="n">
         <v>0.1105876477422001</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
-      <c r="A41">
+    <row r="41">
+      <c r="A41" t="n">
         <v>39</v>
       </c>
-      <c r="B41">
+      <c r="B41" t="n">
         <v>0.1157074462081464</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
-      <c r="A42">
+    <row r="42">
+      <c r="A42" t="n">
         <v>40</v>
       </c>
-      <c r="B42">
+      <c r="B42" t="n">
         <v>0.1210592108693797</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
-      <c r="A43">
+    <row r="43">
+      <c r="A43" t="n">
         <v>41</v>
       </c>
-      <c r="B43">
+      <c r="B43" t="n">
         <v>0.1266517243482454</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
-      <c r="A44">
+    <row r="44">
+      <c r="A44" t="n">
         <v>42</v>
       </c>
-      <c r="B44">
+      <c r="B44" t="n">
         <v>0.1324938987850207</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
-      <c r="A45">
+    <row r="45">
+      <c r="A45" t="n">
         <v>43</v>
       </c>
-      <c r="B45">
+      <c r="B45" t="n">
         <v>0.1385947511427214</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
-      <c r="A46">
+    <row r="46">
+      <c r="A46" t="n">
         <v>44</v>
       </c>
-      <c r="B46">
+      <c r="B46" t="n">
         <v>0.1449633746173355</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
-      <c r="A47">
+    <row r="47">
+      <c r="A47" t="n">
         <v>45</v>
       </c>
-      <c r="B47">
+      <c r="B47" t="n">
         <v>0.1516089058172471</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
-      <c r="A48">
+    <row r="48">
+      <c r="A48" t="n">
         <v>46</v>
       </c>
-      <c r="B48">
+      <c r="B48" t="n">
         <v>0.158540487368153</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
-      <c r="A49">
+    <row r="49">
+      <c r="A49" t="n">
         <v>47</v>
       </c>
-      <c r="B49">
+      <c r="B49" t="n">
         <v>0.1657672255963593</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
-      <c r="A50">
+    <row r="50">
+      <c r="A50" t="n">
         <v>48</v>
       </c>
-      <c r="B50">
+      <c r="B50" t="n">
         <v>0.1732981429449653</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
-      <c r="A51">
+    <row r="51">
+      <c r="A51" t="n">
         <v>49</v>
       </c>
-      <c r="B51">
+      <c r="B51" t="n">
         <v>0.1811421247852415</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
-      <c r="A52">
+    <row r="52">
+      <c r="A52" t="n">
         <v>50</v>
       </c>
-      <c r="B52">
+      <c r="B52" t="n">
         <v>0.1893078603007285</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
-      <c r="A53">
+    <row r="53">
+      <c r="A53" t="n">
         <v>51</v>
       </c>
-      <c r="B53">
+      <c r="B53" t="n">
         <v>0.197803777145623</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
-      <c r="A54">
+    <row r="54">
+      <c r="A54" t="n">
         <v>52</v>
       </c>
-      <c r="B54">
+      <c r="B54" t="n">
         <v>0.2066379696133816</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
-      <c r="A55">
+    <row r="55">
+      <c r="A55" t="n">
         <v>53</v>
       </c>
-      <c r="B55">
+      <c r="B55" t="n">
         <v>0.2158181200977749</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
-      <c r="A56">
+    <row r="56">
+      <c r="A56" t="n">
         <v>54</v>
       </c>
-      <c r="B56">
+      <c r="B56" t="n">
         <v>0.2253514136885641</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
-      <c r="A57">
+    <row r="57">
+      <c r="A57" t="n">
         <v>55</v>
       </c>
-      <c r="B57">
+      <c r="B57" t="n">
         <v>0.2352444458192947</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
-      <c r="A58">
+    <row r="58">
+      <c r="A58" t="n">
         <v>56</v>
       </c>
-      <c r="B58">
+      <c r="B58" t="n">
         <v>0.2455031229771621</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
-      <c r="A59">
+    <row r="59">
+      <c r="A59" t="n">
         <v>57</v>
       </c>
-      <c r="B59">
+      <c r="B59" t="n">
         <v>0.2561325565961908</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
-      <c r="A60">
+    <row r="60">
+      <c r="A60" t="n">
         <v>58</v>
       </c>
-      <c r="B60">
+      <c r="B60" t="n">
         <v>0.2671369503866425</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
-      <c r="A61">
+    <row r="61">
+      <c r="A61" t="n">
         <v>59</v>
       </c>
-      <c r="B61">
+      <c r="B61" t="n">
         <v>0.2785194815069554</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
-      <c r="A62">
+    <row r="62">
+      <c r="A62" t="n">
         <v>60</v>
       </c>
-      <c r="B62">
+      <c r="B62" t="n">
         <v>0.290282176160605</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
-      <c r="A63">
+    <row r="63">
+      <c r="A63" t="n">
         <v>61</v>
       </c>
-      <c r="B63">
+      <c r="B63" t="n">
         <v>0.3024257803995438</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
-      <c r="A64">
+    <row r="64">
+      <c r="A64" t="n">
         <v>62</v>
       </c>
-      <c r="B64">
+      <c r="B64" t="n">
         <v>0.3149496271382108</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
-      <c r="A65">
+    <row r="65">
+      <c r="A65" t="n">
         <v>63</v>
       </c>
-      <c r="B65">
+      <c r="B65" t="n">
         <v>0.3278515006265114</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
-      <c r="A66">
+    <row r="66">
+      <c r="A66" t="n">
         <v>64</v>
       </c>
-      <c r="B66">
+      <c r="B66" t="n">
         <v>0.341127499894705</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
-      <c r="A67">
+    <row r="67">
+      <c r="A67" t="n">
         <v>65</v>
       </c>
-      <c r="B67">
+      <c r="B67" t="n">
         <v>0.3547719029646143</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
-      <c r="A68">
+    <row r="68">
+      <c r="A68" t="n">
         <v>66</v>
       </c>
-      <c r="B68">
+      <c r="B68" t="n">
         <v>0.3687770339153911</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
-      <c r="A69">
+    <row r="69">
+      <c r="A69" t="n">
         <v>67</v>
       </c>
-      <c r="B69">
+      <c r="B69" t="n">
         <v>0.3831331351920205</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
-      <c r="A70">
+    <row r="70">
+      <c r="A70" t="n">
         <v>68</v>
       </c>
-      <c r="B70">
+      <c r="B70" t="n">
         <v>0.3978282478428288</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
-      <c r="A71">
+    <row r="71">
+      <c r="A71" t="n">
         <v>69</v>
       </c>
-      <c r="B71">
+      <c r="B71" t="n">
         <v>0.4128481026585593</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
-      <c r="A72">
+    <row r="72">
+      <c r="A72" t="n">
         <v>70</v>
       </c>
-      <c r="B72">
+      <c r="B72" t="n">
         <v>0.4281760254481776</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
-      <c r="A73">
+    <row r="73">
+      <c r="A73" t="n">
         <v>71</v>
       </c>
-      <c r="B73">
+      <c r="B73" t="n">
         <v>0.4437928599116089</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
-      <c r="A74">
+    <row r="74">
+      <c r="A74" t="n">
         <v>72</v>
       </c>
-      <c r="B74">
+      <c r="B74" t="n">
         <v>0.4596769117413889</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
-      <c r="A75">
+    <row r="75">
+      <c r="A75" t="n">
         <v>73</v>
       </c>
-      <c r="B75">
+      <c r="B75" t="n">
         <v>0.4758039176864697</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
-      <c r="A76">
+    <row r="76">
+      <c r="A76" t="n">
         <v>74</v>
       </c>
-      <c r="B76">
+      <c r="B76" t="n">
         <v>0.4921470433238678</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
-      <c r="A77">
+    <row r="77">
+      <c r="A77" t="n">
         <v>75</v>
       </c>
-      <c r="B77">
+      <c r="B77" t="n">
         <v>0.5086769131886827</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
-      <c r="A78">
+    <row r="78">
+      <c r="A78" t="n">
         <v>76</v>
       </c>
-      <c r="B78">
+      <c r="B78" t="n">
         <v>0.525361676691967</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
-      <c r="A79">
+    <row r="79">
+      <c r="A79" t="n">
         <v>77</v>
       </c>
-      <c r="B79">
+      <c r="B79" t="n">
         <v>0.5421671128922168</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
-      <c r="A80">
+    <row r="80">
+      <c r="A80" t="n">
         <v>78</v>
       </c>
-      <c r="B80">
+      <c r="B80" t="n">
         <v>0.5590567766659129</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
-      <c r="A81">
+    <row r="81">
+      <c r="A81" t="n">
         <v>79</v>
       </c>
-      <c r="B81">
+      <c r="B81" t="n">
         <v>0.5759921881359816</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
-      <c r="A82">
+    <row r="82">
+      <c r="A82" t="n">
         <v>80</v>
       </c>
-      <c r="B82">
+      <c r="B82" t="n">
         <v>0.592933066360474</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
-      <c r="A83">
+    <row r="83">
+      <c r="A83" t="n">
         <v>81</v>
       </c>
-      <c r="B83">
+      <c r="B83" t="n">
         <v>0.6098376072609744</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
-      <c r="A84">
+    <row r="84">
+      <c r="A84" t="n">
         <v>82</v>
       </c>
-      <c r="B84">
+      <c r="B84" t="n">
         <v>0.6266628045939696</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
-      <c r="A85">
+    <row r="85">
+      <c r="A85" t="n">
         <v>83</v>
       </c>
-      <c r="B85">
+      <c r="B85" t="n">
         <v>0.6433648114617025</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
-      <c r="A86">
+    <row r="86">
+      <c r="A86" t="n">
         <v>84</v>
       </c>
-      <c r="B86">
+      <c r="B86" t="n">
         <v>0.6598993384560086</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
-      <c r="A87">
+    <row r="87">
+      <c r="A87" t="n">
         <v>85</v>
       </c>
-      <c r="B87">
+      <c r="B87" t="n">
         <v>0.6762220830748427</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
-      <c r="A88">
+    <row r="88">
+      <c r="A88" t="n">
         <v>86</v>
       </c>
-      <c r="B88">
+      <c r="B88" t="n">
         <v>0.692289183602941</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
-      <c r="A89">
+    <row r="89">
+      <c r="A89" t="n">
         <v>87</v>
       </c>
-      <c r="B89">
+      <c r="B89" t="n">
         <v>0.7080576892710713</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
-      <c r="A90">
+    <row r="90">
+      <c r="A90" t="n">
         <v>88</v>
       </c>
-      <c r="B90">
+      <c r="B90" t="n">
         <v>0.7234860372751407</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
-      <c r="A91">
+    <row r="91">
+      <c r="A91" t="n">
         <v>89</v>
       </c>
-      <c r="B91">
+      <c r="B91" t="n">
         <v>0.7385345262230144</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
-      <c r="A92">
+    <row r="92">
+      <c r="A92" t="n">
         <v>90</v>
       </c>
-      <c r="B92">
+      <c r="B92" t="n">
         <v>0.7531657748579331</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
-      <c r="A93">
+    <row r="93">
+      <c r="A93" t="n">
         <v>91</v>
       </c>
-      <c r="B93">
+      <c r="B93" t="n">
         <v>0.7673451545512801</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
-      <c r="A94">
+    <row r="94">
+      <c r="A94" t="n">
         <v>92</v>
       </c>
-      <c r="B94">
+      <c r="B94" t="n">
         <v>0.7810411841203093</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
-      <c r="A95">
+    <row r="95">
+      <c r="A95" t="n">
         <v>93</v>
       </c>
-      <c r="B95">
+      <c r="B95" t="n">
         <v>0.7942258760468284</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
-      <c r="A96">
+    <row r="96">
+      <c r="A96" t="n">
         <v>94</v>
       </c>
-      <c r="B96">
+      <c r="B96" t="n">
         <v>0.8068750241664815</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
-      <c r="A97">
+    <row r="97">
+      <c r="A97" t="n">
         <v>95</v>
       </c>
-      <c r="B97">
+      <c r="B97" t="n">
         <v>0.8189684243544572</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
-      <c r="A98">
+    <row r="98">
+      <c r="A98" t="n">
         <v>96</v>
       </c>
-      <c r="B98">
+      <c r="B98" t="n">
         <v>0.8304900216129066</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
-      <c r="A99">
+    <row r="99">
+      <c r="A99" t="n">
         <v>97</v>
       </c>
-      <c r="B99">
+      <c r="B99" t="n">
         <v>0.841427979200783</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
-      <c r="A100">
+    <row r="100">
+      <c r="A100" t="n">
         <v>98</v>
       </c>
-      <c r="B100">
+      <c r="B100" t="n">
         <v>0.8517746679457944</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
-      <c r="A101">
+    <row r="101">
+      <c r="A101" t="n">
         <v>99</v>
       </c>
-      <c r="B101">
+      <c r="B101" t="n">
         <v>0.8615265765290623</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
-      <c r="A102">
+    <row r="102">
+      <c r="A102" t="n">
         <v>100</v>
       </c>
-      <c r="B102">
+      <c r="B102" t="n">
         <v>0.8706841462132785</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
-      <c r="A103">
+    <row r="103">
+      <c r="A103" t="n">
         <v>101</v>
       </c>
-      <c r="B103">
+      <c r="B103" t="n">
         <v>0.8792515360716443</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
-      <c r="A104">
+    <row r="104">
+      <c r="A104" t="n">
         <v>102</v>
       </c>
-      <c r="B104">
+      <c r="B104" t="n">
         <v>0.8872363271555272</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
-      <c r="A105">
+    <row r="105">
+      <c r="A105" t="n">
         <v>103</v>
       </c>
-      <c r="B105">
+      <c r="B105" t="n">
         <v>0.8946491761245994</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
-      <c r="A106">
+    <row r="106">
+      <c r="A106" t="n">
         <v>104</v>
       </c>
-      <c r="B106">
+      <c r="B106" t="n">
         <v>0.9015034305985862</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
-      <c r="A107">
+    <row r="107">
+      <c r="A107" t="n">
         <v>105</v>
       </c>
-      <c r="B107">
+      <c r="B107" t="n">
         <v>0.9078147198611326</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
-      <c r="A108">
+    <row r="108">
+      <c r="A108" t="n">
         <v>106</v>
       </c>
-      <c r="B108">
+      <c r="B108" t="n">
         <v>0.9136005355860272</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
-      <c r="A109">
+    <row r="109">
+      <c r="A109" t="n">
         <v>107</v>
       </c>
-      <c r="B109">
+      <c r="B109" t="n">
         <v>0.9188798180405563</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
-      <c r="A110">
+    <row r="110">
+      <c r="A110" t="n">
         <v>108</v>
       </c>
-      <c r="B110">
+      <c r="B110" t="n">
         <v>0.9236725638590978</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
-      <c r="A111">
+    <row r="111">
+      <c r="A111" t="n">
         <v>109</v>
       </c>
-      <c r="B111">
+      <c r="B111" t="n">
         <v>0.9279994720883868</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
-      <c r="A112">
+    <row r="112">
+      <c r="A112" t="n">
         <v>110</v>
       </c>
-      <c r="B112">
+      <c r="B112" t="n">
         <v>0.9318816458603624</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
-      <c r="A113">
+    <row r="113">
+      <c r="A113" t="n">
         <v>111</v>
       </c>
-      <c r="B113">
+      <c r="B113" t="n">
         <v>0.9353403677055223</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
-      <c r="A114">
+    <row r="114">
+      <c r="A114" t="n">
         <v>112</v>
       </c>
-      <c r="B114">
+      <c r="B114" t="n">
         <v>0.9383969668908788</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
-      <c r="A115">
+    <row r="115">
+      <c r="A115" t="n">
         <v>113</v>
       </c>
-      <c r="B115">
+      <c r="B115" t="n">
         <v>0.9410727965391654</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
-      <c r="A116">
+    <row r="116">
+      <c r="A116" t="n">
         <v>114</v>
       </c>
-      <c r="B116">
+      <c r="B116" t="n">
         <v>0.9433893353033589</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
-      <c r="A117">
+    <row r="117">
+      <c r="A117" t="n">
         <v>115</v>
       </c>
-      <c r="B117">
+      <c r="B117" t="n">
         <v>0.9453684208453996</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
-      <c r="A118">
+    <row r="118">
+      <c r="A118" t="n">
         <v>116</v>
       </c>
-      <c r="B118">
+      <c r="B118" t="n">
         <v>0.9470326073258055</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
-      <c r="A119">
+    <row r="119">
+      <c r="A119" t="n">
         <v>117</v>
       </c>
-      <c r="B119">
+      <c r="B119" t="n">
         <v>0.948405613452685</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
-      <c r="A120">
+    <row r="120">
+      <c r="A120" t="n">
         <v>118</v>
       </c>
-      <c r="B120">
+      <c r="B120" t="n">
         <v>0.9495127899841558</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
-      <c r="A121">
+    <row r="121">
+      <c r="A121" t="n">
         <v>119</v>
       </c>
-      <c r="B121">
+      <c r="B121" t="n">
         <v>0.9503814896985835</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
-      <c r="A122">
+    <row r="122">
+      <c r="A122" t="n">
         <v>120</v>
       </c>
-      <c r="B122">
+      <c r="B122" t="n">
         <v>0.9510411820338167</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
-      <c r="A123">
+    <row r="123">
+      <c r="A123" t="n">
         <v>121</v>
       </c>
-      <c r="B123">
+      <c r="B123" t="n">
         <v>0.9515231438742534</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
-      <c r="A124">
+    <row r="124">
+      <c r="A124" t="n">
         <v>122</v>
       </c>
-      <c r="B124">
+      <c r="B124" t="n">
         <v>0.951859608261596</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
-      <c r="A125">
+    <row r="125">
+      <c r="A125" t="n">
         <v>123</v>
       </c>
-      <c r="B125">
+      <c r="B125" t="n">
         <v>0.9520823821744701</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
-      <c r="A126">
+    <row r="126">
+      <c r="A126" t="n">
         <v>124</v>
       </c>
-      <c r="B126">
+      <c r="B126" t="n">
         <v>0.9522211315747523</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
-      <c r="A127">
+    <row r="127">
+      <c r="A127" t="n">
         <v>125</v>
       </c>
-      <c r="B127">
+      <c r="B127" t="n">
         <v>0.9523017031150203</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
-      <c r="A128">
+    <row r="128">
+      <c r="A128" t="n">
         <v>126</v>
       </c>
-      <c r="B128">
+      <c r="B128" t="n">
         <v>0.9523449085090447</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
-      <c r="A129">
+    <row r="129">
+      <c r="A129" t="n">
         <v>127</v>
       </c>
-      <c r="B129">
+      <c r="B129" t="n">
         <v>0.9523660803333406</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
-      <c r="A130">
+    <row r="130">
+      <c r="A130" t="n">
         <v>128</v>
       </c>
-      <c r="B130">
+      <c r="B130" t="n">
         <v>0.952375453391482</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
-      <c r="A131">
+    <row r="131">
+      <c r="A131" t="n">
         <v>129</v>
       </c>
-      <c r="B131">
+      <c r="B131" t="n">
         <v>0.9523809523809523</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/exercisesLifeContingencies/lifeInsurance/makeham_wli.xlsx
+++ b/exercisesLifeContingencies/lifeInsurance/makeham_wli.xlsx
@@ -1,37 +1,54 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="makeham_wli" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="makeham_wli" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>Ax</t>
+  </si>
+  <si>
+    <t>Ax_</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +63,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,1067 +379,1452 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B131"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C131"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>age</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Ax</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
         <v>0.02131339257431903</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
+      <c r="C2">
+        <v>0.02183846773339848</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>0.02216116127381717</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
+      <c r="C3">
+        <v>0.02270708734910754</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4">
         <v>0.02305116984797573</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
+      <c r="C4">
+        <v>0.02361898583241229</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5">
         <v>0.02398549785717418</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="C5">
+        <v>0.02457629390816973</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
         <v>4</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>0.02496632418118079</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="C6">
+        <v>0.02558124406583362</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
         <v>5</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>0.02599593138746477</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
+      <c r="C7">
+        <v>0.02663617503552584</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
         <v>6</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>0.02707671024495758</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
+      <c r="C8">
+        <v>0.02774353641314986</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
         <v>7</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9">
         <v>0.02821116438192677</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
+      <c r="C9">
+        <v>0.02890589343322503</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
         <v>8</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10">
         <v>0.02940191508558346</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
+      <c r="C10">
+        <v>0.03012593188700063</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
         <v>9</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11">
         <v>0.03065170623984182</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
+      <c r="C11">
+        <v>0.03140646318216045</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12">
         <v>10</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12">
         <v>0.03196340939627151</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
+      <c r="C12">
+        <v>0.0327504295390646</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13">
         <v>11</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13">
         <v>0.03334002897171479</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
+      <c r="C13">
+        <v>0.0341609093168419</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14">
         <v>12</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14">
         <v>0.03478470756425205</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
+      <c r="C14">
+        <v>0.03564112246082207</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15">
         <v>13</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15">
         <v>0.03630073137717097</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
+      <c r="C15">
+        <v>0.03719443606072736</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16">
         <v>14</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16">
         <v>0.03789153573830823</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
+      <c r="C16">
+        <v>0.03882437000666317</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17">
         <v>15</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17">
         <v>0.03956071069954484</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
+      <c r="C17">
+        <v>0.04053460272736675</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18">
         <v>16</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18">
         <v>0.04131200669833626</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
+      <c r="C18">
+        <v>0.04232897699213733</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19">
         <v>17</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19">
         <v>0.0431493402599024</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
+      <c r="C19">
+        <v>0.04421150575457011</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20">
         <v>18</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20">
         <v>0.04507679971506211</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
+      <c r="C20">
+        <v>0.04618637801248482</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21">
         <v>19</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21">
         <v>0.04709865090463529</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
+      <c r="C21">
+        <v>0.0482579646542689</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22">
         <v>20</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22">
         <v>0.04921934283681906</v>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
+      <c r="C22">
+        <v>0.05043082425724899</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23">
         <v>21</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23">
         <v>0.05144351325892879</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
+      <c r="C23">
+        <v>0.05270970879854797</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24">
         <v>22</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24">
         <v>0.05377599409934607</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
+      <c r="C24">
+        <v>0.05509956923321591</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25">
         <v>23</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25">
         <v>0.05622181672938697</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
+      <c r="C25">
+        <v>0.05760556088814617</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26">
         <v>24</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26">
         <v>0.05878621698805893</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
+      <c r="C26">
+        <v>0.06023304861331924</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27">
         <v>25</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27">
         <v>0.06147463990526979</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
+      <c r="C27">
+        <v>0.0629876116247734</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28">
         <v>26</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28">
         <v>0.06429274405094447</v>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
+      <c r="C28">
+        <v>0.06587504796388388</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29">
         <v>27</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29">
         <v>0.06724640542866429</v>
       </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
+      <c r="C29">
+        <v>0.06890137849155775</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30">
         <v>28</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30">
         <v>0.07034172082282271</v>
       </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
+      <c r="C30">
+        <v>0.07207285032207433</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31">
         <v>29</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31">
         <v>0.07358501049787318</v>
       </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
+      <c r="C31">
+        <v>0.07539593959417823</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32">
         <v>30</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32">
         <v>0.07698282013699637</v>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
+      <c r="C32">
+        <v>0.07887735346338687</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33">
         <v>31</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33">
         <v>0.08054192189542504</v>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
+      <c r="C33">
+        <v>0.08252403118791796</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34">
         <v>32</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B34">
         <v>0.08426931443073285</v>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
+      <c r="C34">
+        <v>0.08634314488640094</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35">
         <v>33</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B35">
         <v>0.08817222175862861</v>
       </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
+      <c r="C35">
+        <v>0.09034209477851418</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36">
         <v>34</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B36">
         <v>0.09225809076823245</v>
       </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
+      <c r="C36">
+        <v>0.09452851383970862</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37">
         <v>35</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B37">
         <v>0.09653458721549465</v>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
+      <c r="C37">
+        <v>0.0989102565158152</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38">
         <v>36</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B38">
         <v>0.1010095899974369</v>
       </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
+      <c r="C38">
+        <v>0.1034953964640188</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39">
         <v>37</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B39">
         <v>0.1056911834933572</v>
       </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
+      <c r="C39">
+        <v>0.1082922180001886</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40">
         <v>38</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B40">
         <v>0.1105876477422001</v>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
+      <c r="C40">
+        <v>0.1133092060498886</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41">
         <v>39</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B41">
         <v>0.1157074462081464</v>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
+      <c r="C41">
+        <v>0.1185550336302262</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42">
         <v>40</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B42">
         <v>0.1210592108693797</v>
       </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
+      <c r="C42">
+        <v>0.1240385465911286</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43">
         <v>41</v>
       </c>
-      <c r="B43" t="n">
+      <c r="B43">
         <v>0.1266517243482454</v>
       </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
+      <c r="C43">
+        <v>0.1297687453276781</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44">
         <v>42</v>
       </c>
-      <c r="B44" t="n">
+      <c r="B44">
         <v>0.1324938987850207</v>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
+      <c r="C44">
+        <v>0.1357547631586213</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45">
         <v>43</v>
       </c>
-      <c r="B45" t="n">
+      <c r="B45">
         <v>0.1385947511427214</v>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
+      <c r="C45">
+        <v>0.1420058410511875</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46">
         <v>44</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B46">
         <v>0.1449633746173355</v>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
+      <c r="C46">
+        <v>0.1485312983589038</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47">
         <v>45</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B47">
         <v>0.1516089058172471</v>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
+      <c r="C47">
+        <v>0.1553404992284082</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48">
         <v>46</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B48">
         <v>0.158540487368153</v>
       </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
+      <c r="C48">
+        <v>0.1624428143234935</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49">
         <v>47</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B49">
         <v>0.1657672255963593</v>
       </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
+      <c r="C49">
+        <v>0.1698475775113208</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50">
         <v>48</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B50">
         <v>0.1732981429449653</v>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
+      <c r="C50">
+        <v>0.1775640371574115</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51">
         <v>49</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B51">
         <v>0.1811421247852415</v>
       </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
+      <c r="C51">
+        <v>0.1856013016840466</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3">
+      <c r="A52">
         <v>50</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B52">
         <v>0.1893078603007285</v>
       </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
+      <c r="C52">
+        <v>0.1939682790650441</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3">
+      <c r="A53">
         <v>51</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B53">
         <v>0.197803777145623</v>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
+      <c r="C53">
+        <v>0.2026736099329353</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3">
+      <c r="A54">
         <v>52</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B54">
         <v>0.2066379696133816</v>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
+      <c r="C54">
+        <v>0.2117255940893398</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3">
+      <c r="A55">
         <v>53</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B55">
         <v>0.2158181200977749</v>
       </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
+      <c r="C55">
+        <v>0.2211321100897944</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56">
         <v>54</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B56">
         <v>0.2253514136885641</v>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
+      <c r="C56">
+        <v>0.2309005278552871</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57">
         <v>55</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B57">
         <v>0.2352444458192947</v>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
+      <c r="C57">
+        <v>0.2410376141570991</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58">
         <v>56</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B58">
         <v>0.2455031229771621</v>
       </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
+      <c r="C58">
+        <v>0.2515494310090365</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59">
         <v>57</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B59">
         <v>0.2561325565961908</v>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
+      <c r="C59">
+        <v>0.2624412270915558</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60">
         <v>58</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B60">
         <v>0.2671369503866425</v>
       </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
+      <c r="C60">
+        <v>0.2737173224681603</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61">
         <v>59</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B61">
         <v>0.2785194815069554</v>
       </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
+      <c r="C61">
+        <v>0.2853809870123595</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
+      <c r="A62">
         <v>60</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B62">
         <v>0.290282176160605</v>
       </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
+      <c r="C62">
+        <v>0.2974343131445313</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63">
         <v>61</v>
       </c>
-      <c r="B63" t="n">
+      <c r="B63">
         <v>0.3024257803995438</v>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
+      <c r="C63">
+        <v>0.3098780836821342</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64">
         <v>62</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B64">
         <v>0.3149496271382108</v>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
+      <c r="C64">
+        <v>0.3227116358351644</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65">
         <v>63</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B65">
         <v>0.3278515006265114</v>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
+      <c r="C65">
+        <v>0.3359327226292517</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66">
         <v>64</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B66">
         <v>0.341127499894705</v>
       </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
+      <c r="C66">
+        <v>0.3495373733106375</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67">
         <v>65</v>
       </c>
-      <c r="B67" t="n">
+      <c r="B67">
         <v>0.3547719029646143</v>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
+      <c r="C67">
+        <v>0.3635197545757143</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68">
         <v>66</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B68">
         <v>0.3687770339153911</v>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
+      <c r="C68">
+        <v>0.3778720347697695</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69">
         <v>67</v>
       </c>
-      <c r="B69" t="n">
+      <c r="B69">
         <v>0.3831331351920205</v>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
+      <c r="C69">
+        <v>0.3925842535072673</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70">
         <v>68</v>
       </c>
-      <c r="B70" t="n">
+      <c r="B70">
         <v>0.3978282478428288</v>
       </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
+      <c r="C70">
+        <v>0.4076441994722695</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71">
         <v>69</v>
       </c>
-      <c r="B71" t="n">
+      <c r="B71">
         <v>0.4128481026585593</v>
       </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
+      <c r="C71">
+        <v>0.4230372994515147</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72">
         <v>70</v>
       </c>
-      <c r="B72" t="n">
+      <c r="B72">
         <v>0.4281760254481776</v>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
+      <c r="C72">
+        <v>0.4387465219228787</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73">
         <v>71</v>
       </c>
-      <c r="B73" t="n">
+      <c r="B73">
         <v>0.4437928599116089</v>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
+      <c r="C73">
+        <v>0.454752298753054</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74">
         <v>72</v>
       </c>
-      <c r="B74" t="n">
+      <c r="B74">
         <v>0.4596769117413889</v>
       </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
+      <c r="C74">
+        <v>0.4710324687358843</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75">
         <v>73</v>
       </c>
-      <c r="B75" t="n">
+      <c r="B75">
         <v>0.4758039176864697</v>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
+      <c r="C75">
+        <v>0.4875622468073545</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76">
         <v>74</v>
       </c>
-      <c r="B76" t="n">
+      <c r="B76">
         <v>0.4921470433238678</v>
       </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
+      <c r="C76">
+        <v>0.5043142227875714</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77">
         <v>75</v>
       </c>
-      <c r="B77" t="n">
+      <c r="B77">
         <v>0.5086769131886827</v>
       </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
+      <c r="C77">
+        <v>0.5212583934040509</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78">
         <v>76</v>
       </c>
-      <c r="B78" t="n">
+      <c r="B78">
         <v>0.525361676691967</v>
       </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
+      <c r="C78">
+        <v>0.538362231125875</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79">
         <v>77</v>
       </c>
-      <c r="B79" t="n">
+      <c r="B79">
         <v>0.5421671128922168</v>
       </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
+      <c r="C79">
+        <v>0.5555907929675706</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80">
         <v>78</v>
       </c>
-      <c r="B80" t="n">
+      <c r="B80">
         <v>0.5590567766659129</v>
       </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
+      <c r="C80">
+        <v>0.5729068718905337</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81">
         <v>79</v>
       </c>
-      <c r="B81" t="n">
+      <c r="B81">
         <v>0.5759921881359816</v>
       </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
+      <c r="C81">
+        <v>0.5902711927289979</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82">
         <v>80</v>
       </c>
-      <c r="B82" t="n">
+      <c r="B82">
         <v>0.592933066360474</v>
       </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
+      <c r="C82">
+        <v>0.6076426536922175</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83">
         <v>81</v>
       </c>
-      <c r="B83" t="n">
+      <c r="B83">
         <v>0.6098376072609744</v>
       </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
+      <c r="C83">
+        <v>0.6249786134500703</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84">
         <v>82</v>
       </c>
-      <c r="B84" t="n">
+      <c r="B84">
         <v>0.6266628045939696</v>
       </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
+      <c r="C84">
+        <v>0.6422352226071124</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85">
         <v>83</v>
       </c>
-      <c r="B85" t="n">
+      <c r="B85">
         <v>0.6433648114617025</v>
       </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
+      <c r="C85">
+        <v>0.6593677970349821</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86">
         <v>84</v>
       </c>
-      <c r="B86" t="n">
+      <c r="B86">
         <v>0.6598993384560086</v>
       </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
+      <c r="C86">
+        <v>0.6763312290997248</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87">
         <v>85</v>
       </c>
-      <c r="B87" t="n">
+      <c r="B87">
         <v>0.6762220830748427</v>
       </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
+      <c r="C87">
+        <v>0.6930804313355352</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88">
         <v>86</v>
       </c>
-      <c r="B88" t="n">
+      <c r="B88">
         <v>0.692289183602941</v>
       </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
+      <c r="C88">
+        <v>0.7095708056367056</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89">
         <v>87</v>
       </c>
-      <c r="B89" t="n">
+      <c r="B89">
         <v>0.7080576892710713</v>
       </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
+      <c r="C89">
+        <v>0.725758729635308</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90">
         <v>88</v>
       </c>
-      <c r="B90" t="n">
+      <c r="B90">
         <v>0.7234860372751407</v>
       </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
+      <c r="C90">
+        <v>0.7416020506721074</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91">
         <v>89</v>
       </c>
-      <c r="B91" t="n">
+      <c r="B91">
         <v>0.7385345262230144</v>
       </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="n">
+      <c r="C91">
+        <v>0.7570605767369721</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92">
         <v>90</v>
       </c>
-      <c r="B92" t="n">
+      <c r="B92">
         <v>0.7531657748579331</v>
       </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="n">
+      <c r="C92">
+        <v>0.7720965530230101</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93">
         <v>91</v>
       </c>
-      <c r="B93" t="n">
+      <c r="B93">
         <v>0.7673451545512801</v>
       </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="n">
+      <c r="C93">
+        <v>0.7866751123789689</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94">
         <v>92</v>
       </c>
-      <c r="B94" t="n">
+      <c r="B94">
         <v>0.7810411841203093</v>
       </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n">
+      <c r="C94">
+        <v>0.8007646880128469</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95">
         <v>93</v>
       </c>
-      <c r="B95" t="n">
+      <c r="B95">
         <v>0.7942258760468284</v>
       </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
+      <c r="C95">
+        <v>0.8143373773350518</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96">
         <v>94</v>
       </c>
-      <c r="B96" t="n">
+      <c r="B96">
         <v>0.8068750241664815</v>
       </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="n">
+      <c r="C96">
+        <v>0.827369246846828</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97">
         <v>95</v>
       </c>
-      <c r="B97" t="n">
+      <c r="B97">
         <v>0.8189684243544572</v>
       </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="n">
+      <c r="C97">
+        <v>0.8398405694662308</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98">
         <v>96</v>
       </c>
-      <c r="B98" t="n">
+      <c r="B98">
         <v>0.8304900216129066</v>
       </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="n">
+      <c r="C98">
+        <v>0.8517359875969845</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99">
         <v>97</v>
       </c>
-      <c r="B99" t="n">
+      <c r="B99">
         <v>0.841427979200783</v>
       </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="n">
+      <c r="C99">
+        <v>0.8630445975125538</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100">
         <v>98</v>
       </c>
-      <c r="B100" t="n">
+      <c r="B100">
         <v>0.8517746679457944</v>
       </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="n">
+      <c r="C100">
+        <v>0.8737599531487861</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101">
         <v>99</v>
       </c>
-      <c r="B101" t="n">
+      <c r="B101">
         <v>0.8615265765290623</v>
       </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="n">
+      <c r="C101">
+        <v>0.8838799900519639</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102">
         <v>100</v>
       </c>
-      <c r="B102" t="n">
+      <c r="B102">
         <v>0.8706841462132785</v>
       </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="n">
+      <c r="C102">
+        <v>0.8934068728791764</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103">
         <v>101</v>
       </c>
-      <c r="B103" t="n">
+      <c r="B103">
         <v>0.8792515360716443</v>
       </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="n">
+      <c r="C103">
+        <v>0.9023467723543033</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104">
         <v>102</v>
       </c>
-      <c r="B104" t="n">
+      <c r="B104">
         <v>0.8872363271555272</v>
       </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="n">
+      <c r="C104">
+        <v>0.9107095798114119</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105">
         <v>103</v>
       </c>
-      <c r="B105" t="n">
+      <c r="B105">
         <v>0.8946491761245994</v>
       </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="n">
+      <c r="C105">
+        <v>0.9185085692903686</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106">
         <v>104</v>
       </c>
-      <c r="B106" t="n">
+      <c r="B106">
         <v>0.9015034305985862</v>
       </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="n">
+      <c r="C106">
+        <v>0.9257600184956263</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107">
         <v>105</v>
       </c>
-      <c r="B107" t="n">
+      <c r="B107">
         <v>0.9078147198611326</v>
       </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="n">
+      <c r="C107">
+        <v>0.9324828007298374</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108">
         <v>106</v>
       </c>
-      <c r="B108" t="n">
+      <c r="B108">
         <v>0.9136005355860272</v>
       </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="n">
+      <c r="C108">
+        <v>0.9386979601485927</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109">
         <v>107</v>
       </c>
-      <c r="B109" t="n">
+      <c r="B109">
         <v>0.9188798180405563</v>
       </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="n">
+      <c r="C109">
+        <v>0.9444282823679473</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110">
         <v>108</v>
       </c>
-      <c r="B110" t="n">
+      <c r="B110">
         <v>0.9236725638590978</v>
       </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n">
+      <c r="C110">
+        <v>0.9496978716448743</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111">
         <v>109</v>
       </c>
-      <c r="B111" t="n">
+      <c r="B111">
         <v>0.9279994720883868</v>
       </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="n">
+      <c r="C111">
+        <v>0.9545317446237099</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112">
         <v>110</v>
       </c>
-      <c r="B112" t="n">
+      <c r="B112">
         <v>0.9318816458603624</v>
       </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="n">
+      <c r="C112">
+        <v>0.958955449101193</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113">
         <v>111</v>
       </c>
-      <c r="B113" t="n">
+      <c r="B113">
         <v>0.9353403677055223</v>
       </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
+      <c r="C113">
+        <v>0.9629947145221771</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114">
         <v>112</v>
       </c>
-      <c r="B114" t="n">
+      <c r="B114">
         <v>0.9383969668908788</v>
       </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
+      <c r="C114">
+        <v>0.9666751390920042</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115">
         <v>113</v>
       </c>
-      <c r="B115" t="n">
+      <c r="B115">
         <v>0.9410727965391654</v>
       </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
+      <c r="C115">
+        <v>0.9700219165866659</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116">
         <v>114</v>
       </c>
-      <c r="B116" t="n">
+      <c r="B116">
         <v>0.9433893353033589</v>
       </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
+      <c r="C116">
+        <v>0.973059604249833</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117">
         <v>115</v>
       </c>
-      <c r="B117" t="n">
+      <c r="B117">
         <v>0.9453684208453996</v>
       </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
+      <c r="C117">
+        <v>0.9758119316584863</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118">
         <v>116</v>
       </c>
-      <c r="B118" t="n">
+      <c r="B118">
         <v>0.9470326073258055</v>
       </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
+      <c r="C118">
+        <v>0.9783016491651689</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119">
         <v>117</v>
       </c>
-      <c r="B119" t="n">
+      <c r="B119">
         <v>0.948405613452685</v>
       </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
+      <c r="C119">
+        <v>0.9805504135116315</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120">
         <v>118</v>
       </c>
-      <c r="B120" t="n">
+      <c r="B120">
         <v>0.9495127899841558</v>
       </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
+      <c r="C120">
+        <v>0.9825787074617135</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121">
         <v>119</v>
       </c>
-      <c r="B121" t="n">
+      <c r="B121">
         <v>0.9503814896985835</v>
       </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
+      <c r="C121">
+        <v>0.9844057898093281</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122">
         <v>120</v>
       </c>
-      <c r="B122" t="n">
+      <c r="B122">
         <v>0.9510411820338167</v>
       </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n">
+      <c r="C122">
+        <v>0.9860496718562833</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123">
         <v>121</v>
       </c>
-      <c r="B123" t="n">
+      <c r="B123">
         <v>0.9515231438742534</v>
       </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="n">
+      <c r="C123">
+        <v>0.9875271163905259</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124">
         <v>122</v>
       </c>
-      <c r="B124" t="n">
+      <c r="B124">
         <v>0.951859608261596</v>
       </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="n">
+      <c r="C124">
+        <v>0.9888536552920273</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125">
         <v>123</v>
       </c>
-      <c r="B125" t="n">
+      <c r="B125">
         <v>0.9520823821744701</v>
       </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="n">
+      <c r="C125">
+        <v>0.9900436221109798</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126">
         <v>124</v>
       </c>
-      <c r="B126" t="n">
+      <c r="B126">
         <v>0.9522211315747523</v>
       </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="n">
+      <c r="C126">
+        <v>0.9911101962660576</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127">
         <v>125</v>
       </c>
-      <c r="B127" t="n">
+      <c r="B127">
         <v>0.9523017031150203</v>
       </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="n">
+      <c r="C127">
+        <v>0.9920654558659634</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128">
         <v>126</v>
       </c>
-      <c r="B128" t="n">
+      <c r="B128">
         <v>0.9523449085090447</v>
       </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
+      <c r="C128">
+        <v>0.9929204365380463</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129">
         <v>127</v>
       </c>
-      <c r="B129" t="n">
+      <c r="B129">
         <v>0.9523660803333406</v>
       </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
+      <c r="C129">
+        <v>0.9936851940313892</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130">
         <v>128</v>
       </c>
-      <c r="B130" t="n">
+      <c r="B130">
         <v>0.952375453391482</v>
       </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
+      <c r="C130">
+        <v>0.9943688687318274</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131">
         <v>129</v>
       </c>
-      <c r="B131" t="n">
+      <c r="B131">
         <v>0.9523809523809523</v>
       </c>
+      <c r="C131">
+        <v>0.9949797505712356</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>